--- a/artfynd/A 43906-2025 artfynd.xlsx
+++ b/artfynd/A 43906-2025 artfynd.xlsx
@@ -758,61 +758,62 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910386</v>
+        <v>129910384</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>92881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvisthån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451003</v>
+        <v>450931</v>
       </c>
       <c r="R3" t="n">
-        <v>6914431</v>
+        <v>6914453</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,52 +855,71 @@
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910384</v>
+        <v>129910386</v>
       </c>
       <c r="B4" t="n">
-        <v>92881</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvisthån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450931</v>
+        <v>451003</v>
       </c>
       <c r="R4" t="n">
-        <v>6914453</v>
+        <v>6914431</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -941,6 +961,16 @@
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1040,6 +1070,16 @@
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 43906-2025 artfynd.xlsx
+++ b/artfynd/A 43906-2025 artfynd.xlsx
@@ -772,48 +772,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910384</v>
+        <v>129910386</v>
       </c>
       <c r="B3" t="n">
-        <v>92881</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvisthån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450931</v>
+        <v>451003</v>
       </c>
       <c r="R3" t="n">
-        <v>6914453</v>
+        <v>6914431</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,57 +878,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910386</v>
+        <v>129910384</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>92881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvisthån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451003</v>
+        <v>450931</v>
       </c>
       <c r="R4" t="n">
-        <v>6914431</v>
+        <v>6914453</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 43906-2025 artfynd.xlsx
+++ b/artfynd/A 43906-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910385</v>
       </c>
       <c r="B2" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,57 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910386</v>
+        <v>129910384</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>92884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvisthån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451003</v>
+        <v>450931</v>
       </c>
       <c r="R3" t="n">
-        <v>6914431</v>
+        <v>6914453</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,48 +869,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910384</v>
+        <v>129910386</v>
       </c>
       <c r="B4" t="n">
-        <v>92881</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvisthån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450931</v>
+        <v>451003</v>
       </c>
       <c r="R4" t="n">
-        <v>6914453</v>
+        <v>6914431</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129910387</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43906-2025 artfynd.xlsx
+++ b/artfynd/A 43906-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910385</v>
       </c>
       <c r="B2" t="n">
-        <v>83055</v>
+        <v>83058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129910384</v>
       </c>
       <c r="B3" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129910386</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129910387</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43906-2025 artfynd.xlsx
+++ b/artfynd/A 43906-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910385</v>
       </c>
       <c r="B2" t="n">
-        <v>83058</v>
+        <v>83059</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129910384</v>
       </c>
       <c r="B3" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43906-2025 artfynd.xlsx
+++ b/artfynd/A 43906-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910385</v>
       </c>
       <c r="B2" t="n">
-        <v>83059</v>
+        <v>83065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129910384</v>
       </c>
       <c r="B3" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129910386</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43906-2025 artfynd.xlsx
+++ b/artfynd/A 43906-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129910384</v>
       </c>
       <c r="B3" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43906-2025 artfynd.xlsx
+++ b/artfynd/A 43906-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910385</v>
       </c>
       <c r="B2" t="n">
-        <v>83073</v>
+        <v>83158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129910384</v>
       </c>
       <c r="B3" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129910386</v>
       </c>
       <c r="B4" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129910387</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43906-2025 artfynd.xlsx
+++ b/artfynd/A 43906-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910385</v>
       </c>
       <c r="B2" t="n">
-        <v>83158</v>
+        <v>83073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129910384</v>
       </c>
       <c r="B3" t="n">
-        <v>93010</v>
+        <v>92923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129910386</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>57900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129910387</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43906-2025 artfynd.xlsx
+++ b/artfynd/A 43906-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910385</v>
+        <v>129910384</v>
       </c>
       <c r="B2" t="n">
-        <v>83158</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450800</v>
+        <v>450931</v>
       </c>
       <c r="R2" t="n">
-        <v>6914365</v>
+        <v>6914453</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910384</v>
+        <v>129910385</v>
       </c>
       <c r="B3" t="n">
-        <v>93010</v>
+        <v>83307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450931</v>
+        <v>450800</v>
       </c>
       <c r="R3" t="n">
-        <v>6914453</v>
+        <v>6914365</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910386</v>
+        <v>129910387</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,33 +880,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvisthån, Hjd</t>
@@ -963,22 +966,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910387</v>
+        <v>129910386</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,36 +989,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvisthån, Hjd</t>
@@ -1072,12 +1072,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 43906-2025 artfynd.xlsx
+++ b/artfynd/A 43906-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910384</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910385</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910387</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,8 +1101,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910386</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>